--- a/PD.xlsx
+++ b/PD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stoces\Documents\Cesky_Hradek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56047DEB-0879-4CD3-9272-5A2047DBF24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2206EF-A969-4FED-ACC2-C4EE39374BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="19">
   <si>
     <t>Year</t>
   </si>
@@ -65,17 +65,49 @@
   <si>
     <t>ID</t>
   </si>
+  <si>
+    <t>Elevation_Group</t>
+  </si>
+  <si>
+    <t>Exposition_Group</t>
+  </si>
+  <si>
+    <t>resid</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -99,9 +131,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -382,15 +417,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K298"/>
+  <dimension ref="A1:N298"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.88671875" style="1"/>
     <col min="9" max="9" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -424,8 +462,17 @@
       <c r="K1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -459,8 +506,17 @@
       <c r="K2">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2">
+        <v>-7.3422648294365289E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -494,8 +550,17 @@
       <c r="K3">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3">
+        <v>0.17202670259840411</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -529,8 +594,17 @@
       <c r="K4">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4">
+        <v>9.6314940423504858E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -564,8 +638,17 @@
       <c r="K5">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5">
+        <v>-7.590679836845049E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -599,8 +682,17 @@
       <c r="K6">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6">
+        <v>-7.564164630685466E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -634,8 +726,17 @@
       <c r="K7">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7">
+        <v>7.8701223700235134E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -669,8 +770,17 @@
       <c r="K8">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8">
+        <v>9.6436923218893189E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -704,8 +814,17 @@
       <c r="K9">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>16</v>
+      </c>
+      <c r="N9">
+        <v>-9.8777884962613416E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -739,8 +858,17 @@
       <c r="K10">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10">
+        <v>6.3346722725192373E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -774,8 +902,17 @@
       <c r="K11">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11">
+        <v>-7.702388952966821E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -809,8 +946,17 @@
       <c r="K12">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12">
+        <v>3.4617719712122463E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -844,8 +990,17 @@
       <c r="K13">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" t="s">
+        <v>16</v>
+      </c>
+      <c r="N13">
+        <v>0.164253175237983</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -879,8 +1034,17 @@
       <c r="K14">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M14" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14">
+        <v>-8.9547574682248721E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -914,8 +1078,17 @@
       <c r="K15">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M15" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15">
+        <v>-0.29601456715100399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -949,8 +1122,17 @@
       <c r="K16">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+      <c r="M16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N16">
+        <v>-0.33194406188539932</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -984,8 +1166,17 @@
       <c r="K17">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" t="s">
+        <v>16</v>
+      </c>
+      <c r="N17">
+        <v>5.9060686336847468E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1019,8 +1210,17 @@
       <c r="K18">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18" t="s">
+        <v>15</v>
+      </c>
+      <c r="N18">
+        <v>-0.1535989589909437</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1054,8 +1254,17 @@
       <c r="K19">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19">
+        <v>1.6613690892395731E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1089,8 +1298,17 @@
       <c r="K20">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" t="s">
+        <v>14</v>
+      </c>
+      <c r="M20" t="s">
+        <v>15</v>
+      </c>
+      <c r="N20">
+        <v>-0.13779383326471761</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1124,8 +1342,17 @@
       <c r="K21">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" t="s">
+        <v>14</v>
+      </c>
+      <c r="M21" t="s">
+        <v>16</v>
+      </c>
+      <c r="N21">
+        <v>-0.22999537233127831</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1159,8 +1386,17 @@
       <c r="K22">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" t="s">
+        <v>14</v>
+      </c>
+      <c r="M22" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22">
+        <v>9.6259074753057838E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1194,8 +1430,17 @@
       <c r="K23">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" t="s">
+        <v>15</v>
+      </c>
+      <c r="N23">
+        <v>-0.16279845155935291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1229,8 +1474,17 @@
       <c r="K24">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" t="s">
+        <v>15</v>
+      </c>
+      <c r="N24">
+        <v>6.5608566556777936E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1264,8 +1518,17 @@
       <c r="K25">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N25">
+        <v>4.9249410131562699E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1299,8 +1562,17 @@
       <c r="K26">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" t="s">
+        <v>18</v>
+      </c>
+      <c r="M26" t="s">
+        <v>16</v>
+      </c>
+      <c r="N26">
+        <v>4.2962442838950787E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1334,8 +1606,17 @@
       <c r="K27">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" t="s">
+        <v>16</v>
+      </c>
+      <c r="N27">
+        <v>-2.0041259897842782E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1369,8 +1650,17 @@
       <c r="K28">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" t="s">
+        <v>17</v>
+      </c>
+      <c r="M28" t="s">
+        <v>15</v>
+      </c>
+      <c r="N28">
+        <v>0.16431299336179009</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1404,8 +1694,17 @@
       <c r="K29">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" t="s">
+        <v>17</v>
+      </c>
+      <c r="M29" t="s">
+        <v>15</v>
+      </c>
+      <c r="N29">
+        <v>1.108115905813889E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1439,8 +1738,17 @@
       <c r="K30">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30" t="s">
+        <v>18</v>
+      </c>
+      <c r="M30" t="s">
+        <v>15</v>
+      </c>
+      <c r="N30">
+        <v>0.10686113331701599</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1474,8 +1782,17 @@
       <c r="K31">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" t="s">
+        <v>14</v>
+      </c>
+      <c r="M31" t="s">
+        <v>16</v>
+      </c>
+      <c r="N31">
+        <v>0.1275345970144636</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1509,8 +1826,17 @@
       <c r="K32">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" t="s">
+        <v>14</v>
+      </c>
+      <c r="M32" t="s">
+        <v>16</v>
+      </c>
+      <c r="N32">
+        <v>0.16088382056779801</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1544,8 +1870,17 @@
       <c r="K33">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" t="s">
+        <v>17</v>
+      </c>
+      <c r="M33" t="s">
+        <v>15</v>
+      </c>
+      <c r="N33">
+        <v>-0.32771208671808738</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1579,8 +1914,17 @@
       <c r="K34">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34" t="s">
+        <v>17</v>
+      </c>
+      <c r="M34" t="s">
+        <v>15</v>
+      </c>
+      <c r="N34">
+        <v>-5.251305842877374E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1614,8 +1958,17 @@
       <c r="K35">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35" t="s">
+        <v>18</v>
+      </c>
+      <c r="M35" t="s">
+        <v>16</v>
+      </c>
+      <c r="N35">
+        <v>-9.2097181901956038E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1649,8 +2002,17 @@
       <c r="K36">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M36" t="s">
+        <v>15</v>
+      </c>
+      <c r="N36">
+        <v>-0.20340604685314009</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1684,8 +2046,17 @@
       <c r="K37">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37" t="s">
+        <v>17</v>
+      </c>
+      <c r="M37" t="s">
+        <v>16</v>
+      </c>
+      <c r="N37">
+        <v>0.2598948828506582</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1719,8 +2090,17 @@
       <c r="K38">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38" t="s">
+        <v>14</v>
+      </c>
+      <c r="M38" t="s">
+        <v>15</v>
+      </c>
+      <c r="N38">
+        <v>8.2294132058213565E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1754,8 +2134,17 @@
       <c r="K39">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39" t="s">
+        <v>14</v>
+      </c>
+      <c r="M39" t="s">
+        <v>16</v>
+      </c>
+      <c r="N39">
+        <v>7.4698701129798817E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1789,8 +2178,17 @@
       <c r="K40">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40" t="s">
+        <v>14</v>
+      </c>
+      <c r="M40" t="s">
+        <v>16</v>
+      </c>
+      <c r="N40">
+        <v>0.1214450701663837</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1824,8 +2222,17 @@
       <c r="K41">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41" t="s">
+        <v>17</v>
+      </c>
+      <c r="M41" t="s">
+        <v>15</v>
+      </c>
+      <c r="N41">
+        <v>3.1741687480039249E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1859,8 +2266,17 @@
       <c r="K42">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42" t="s">
+        <v>17</v>
+      </c>
+      <c r="M42" t="s">
+        <v>15</v>
+      </c>
+      <c r="N42">
+        <v>1.3933432936234171E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1894,8 +2310,17 @@
       <c r="K43">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43" t="s">
+        <v>18</v>
+      </c>
+      <c r="M43" t="s">
+        <v>15</v>
+      </c>
+      <c r="N43">
+        <v>1.049178103067594E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1929,8 +2354,17 @@
       <c r="K44">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44" t="s">
+        <v>18</v>
+      </c>
+      <c r="M44" t="s">
+        <v>16</v>
+      </c>
+      <c r="N44">
+        <v>0.21250146181527821</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1964,8 +2398,17 @@
       <c r="K45">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45" t="s">
+        <v>18</v>
+      </c>
+      <c r="M45" t="s">
+        <v>16</v>
+      </c>
+      <c r="N45">
+        <v>4.7776082332440462E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1999,8 +2442,17 @@
       <c r="K46">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46" t="s">
+        <v>17</v>
+      </c>
+      <c r="M46" t="s">
+        <v>15</v>
+      </c>
+      <c r="N46">
+        <v>8.1050706707475273E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2034,8 +2486,17 @@
       <c r="K47">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47" t="s">
+        <v>17</v>
+      </c>
+      <c r="M47" t="s">
+        <v>15</v>
+      </c>
+      <c r="N47">
+        <v>1.815303326763618E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2069,8 +2530,17 @@
       <c r="K48">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48" t="s">
+        <v>18</v>
+      </c>
+      <c r="M48" t="s">
+        <v>15</v>
+      </c>
+      <c r="N48">
+        <v>0.12726730633309319</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2104,8 +2574,17 @@
       <c r="K49">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49" t="s">
+        <v>14</v>
+      </c>
+      <c r="M49" t="s">
+        <v>16</v>
+      </c>
+      <c r="N49">
+        <v>4.3344277365990669E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2139,8 +2618,17 @@
       <c r="K50">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L50" t="s">
+        <v>14</v>
+      </c>
+      <c r="M50" t="s">
+        <v>16</v>
+      </c>
+      <c r="N50">
+        <v>0.1860092263079052</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2174,8 +2662,17 @@
       <c r="K51">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L51" t="s">
+        <v>17</v>
+      </c>
+      <c r="M51" t="s">
+        <v>15</v>
+      </c>
+      <c r="N51">
+        <v>6.0359885372017752E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2209,8 +2706,17 @@
       <c r="K52">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L52" t="s">
+        <v>17</v>
+      </c>
+      <c r="M52" t="s">
+        <v>15</v>
+      </c>
+      <c r="N52">
+        <v>-3.1757206493435497E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2244,8 +2750,17 @@
       <c r="K53">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L53" t="s">
+        <v>18</v>
+      </c>
+      <c r="M53" t="s">
+        <v>16</v>
+      </c>
+      <c r="N53">
+        <v>-3.2529593887480779E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2279,8 +2794,17 @@
       <c r="K54">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L54" t="s">
+        <v>17</v>
+      </c>
+      <c r="M54" t="s">
+        <v>15</v>
+      </c>
+      <c r="N54">
+        <v>-2.687832770435394E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2314,8 +2838,17 @@
       <c r="K55">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L55" t="s">
+        <v>17</v>
+      </c>
+      <c r="M55" t="s">
+        <v>16</v>
+      </c>
+      <c r="N55">
+        <v>-2.0786327961674681E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2349,8 +2882,17 @@
       <c r="K56">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L56" t="s">
+        <v>14</v>
+      </c>
+      <c r="M56" t="s">
+        <v>15</v>
+      </c>
+      <c r="N56">
+        <v>-6.4873906562798012E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2384,8 +2926,17 @@
       <c r="K57">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L57" t="s">
+        <v>14</v>
+      </c>
+      <c r="M57" t="s">
+        <v>16</v>
+      </c>
+      <c r="N57">
+        <v>-0.28945573078861558</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2419,8 +2970,17 @@
       <c r="K58">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L58" t="s">
+        <v>14</v>
+      </c>
+      <c r="M58" t="s">
+        <v>16</v>
+      </c>
+      <c r="N58">
+        <v>-7.9264186166367878E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2454,8 +3014,17 @@
       <c r="K59">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L59" t="s">
+        <v>17</v>
+      </c>
+      <c r="M59" t="s">
+        <v>15</v>
+      </c>
+      <c r="N59">
+        <v>0.35292597101216061</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2489,8 +3058,17 @@
       <c r="K60">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L60" t="s">
+        <v>17</v>
+      </c>
+      <c r="M60" t="s">
+        <v>15</v>
+      </c>
+      <c r="N60">
+        <v>-9.8423719413837429E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2524,8 +3102,17 @@
       <c r="K61">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L61" t="s">
+        <v>18</v>
+      </c>
+      <c r="M61" t="s">
+        <v>15</v>
+      </c>
+      <c r="N61">
+        <v>1.1804581664501381E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>63</v>
       </c>
@@ -2559,8 +3146,17 @@
       <c r="K62">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L62" t="s">
+        <v>17</v>
+      </c>
+      <c r="M62" t="s">
+        <v>15</v>
+      </c>
+      <c r="N62">
+        <v>5.2170172933343813E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>64</v>
       </c>
@@ -2594,8 +3190,17 @@
       <c r="K63">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L63" t="s">
+        <v>17</v>
+      </c>
+      <c r="M63" t="s">
+        <v>15</v>
+      </c>
+      <c r="N63">
+        <v>-5.3881287663752442E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>65</v>
       </c>
@@ -2629,8 +3234,17 @@
       <c r="K64">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L64" t="s">
+        <v>18</v>
+      </c>
+      <c r="M64" t="s">
+        <v>15</v>
+      </c>
+      <c r="N64">
+        <v>0.12322908032934669</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>66</v>
       </c>
@@ -2664,8 +3278,17 @@
       <c r="K65">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L65" t="s">
+        <v>14</v>
+      </c>
+      <c r="M65" t="s">
+        <v>16</v>
+      </c>
+      <c r="N65">
+        <v>-0.1091284036220348</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>67</v>
       </c>
@@ -2699,8 +3322,17 @@
       <c r="K66">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L66" t="s">
+        <v>14</v>
+      </c>
+      <c r="M66" t="s">
+        <v>16</v>
+      </c>
+      <c r="N66">
+        <v>-0.1111651745129483</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>68</v>
       </c>
@@ -2734,8 +3366,17 @@
       <c r="K67">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L67" t="s">
+        <v>17</v>
+      </c>
+      <c r="M67" t="s">
+        <v>15</v>
+      </c>
+      <c r="N67">
+        <v>-0.33571993121601429</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>69</v>
       </c>
@@ -2769,8 +3410,17 @@
       <c r="K68">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L68" t="s">
+        <v>17</v>
+      </c>
+      <c r="M68" t="s">
+        <v>15</v>
+      </c>
+      <c r="N68">
+        <v>5.4329479498807953E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>70</v>
       </c>
@@ -2804,8 +3454,17 @@
       <c r="K69">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L69" t="s">
+        <v>18</v>
+      </c>
+      <c r="M69" t="s">
+        <v>16</v>
+      </c>
+      <c r="N69">
+        <v>0.27222201277180469</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>71</v>
       </c>
@@ -2839,8 +3498,17 @@
       <c r="K70">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L70" t="s">
+        <v>17</v>
+      </c>
+      <c r="M70" t="s">
+        <v>15</v>
+      </c>
+      <c r="N70">
+        <v>0.37904582164429762</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>72</v>
       </c>
@@ -2874,8 +3542,17 @@
       <c r="K71">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L71" t="s">
+        <v>17</v>
+      </c>
+      <c r="M71" t="s">
+        <v>16</v>
+      </c>
+      <c r="N71">
+        <v>0.36659581925742879</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>73</v>
       </c>
@@ -2909,8 +3586,17 @@
       <c r="K72">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L72" t="s">
+        <v>14</v>
+      </c>
+      <c r="M72" t="s">
+        <v>15</v>
+      </c>
+      <c r="N72">
+        <v>0.2050389287051011</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>74</v>
       </c>
@@ -2944,8 +3630,17 @@
       <c r="K73">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L73" t="s">
+        <v>14</v>
+      </c>
+      <c r="M73" t="s">
+        <v>16</v>
+      </c>
+      <c r="N73">
+        <v>0.1503311884011754</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>75</v>
       </c>
@@ -2979,8 +3674,17 @@
       <c r="K74">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L74" t="s">
+        <v>14</v>
+      </c>
+      <c r="M74" t="s">
+        <v>16</v>
+      </c>
+      <c r="N74">
+        <v>6.9304815200696201E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>76</v>
       </c>
@@ -3014,8 +3718,17 @@
       <c r="K75">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L75" t="s">
+        <v>17</v>
+      </c>
+      <c r="M75" t="s">
+        <v>15</v>
+      </c>
+      <c r="N75">
+        <v>0.1140782736232188</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>77</v>
       </c>
@@ -3049,8 +3762,17 @@
       <c r="K76">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L76" t="s">
+        <v>17</v>
+      </c>
+      <c r="M76" t="s">
+        <v>15</v>
+      </c>
+      <c r="N76">
+        <v>-5.6892886222779222E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>78</v>
       </c>
@@ -3084,8 +3806,17 @@
       <c r="K77">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L77" t="s">
+        <v>18</v>
+      </c>
+      <c r="M77" t="s">
+        <v>15</v>
+      </c>
+      <c r="N77">
+        <v>0.1971988043609065</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>79</v>
       </c>
@@ -3119,8 +3850,17 @@
       <c r="K78">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L78" t="s">
+        <v>18</v>
+      </c>
+      <c r="M78" t="s">
+        <v>16</v>
+      </c>
+      <c r="N78">
+        <v>0.1322515503737387</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>80</v>
       </c>
@@ -3154,8 +3894,17 @@
       <c r="K79">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L79" t="s">
+        <v>18</v>
+      </c>
+      <c r="M79" t="s">
+        <v>16</v>
+      </c>
+      <c r="N79">
+        <v>-0.105021216650276</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>81</v>
       </c>
@@ -3189,8 +3938,17 @@
       <c r="K80">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L80" t="s">
+        <v>17</v>
+      </c>
+      <c r="M80" t="s">
+        <v>15</v>
+      </c>
+      <c r="N80">
+        <v>0.19534791419312891</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>82</v>
       </c>
@@ -3224,8 +3982,17 @@
       <c r="K81">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L81" t="s">
+        <v>17</v>
+      </c>
+      <c r="M81" t="s">
+        <v>15</v>
+      </c>
+      <c r="N81">
+        <v>0.13739950787882371</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>83</v>
       </c>
@@ -3259,8 +4026,17 @@
       <c r="K82">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L82" t="s">
+        <v>18</v>
+      </c>
+      <c r="M82" t="s">
+        <v>15</v>
+      </c>
+      <c r="N82">
+        <v>4.6559536744044887E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>84</v>
       </c>
@@ -3294,8 +4070,17 @@
       <c r="K83">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L83" t="s">
+        <v>14</v>
+      </c>
+      <c r="M83" t="s">
+        <v>16</v>
+      </c>
+      <c r="N83">
+        <v>0.31013970959862042</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>85</v>
       </c>
@@ -3329,8 +4114,17 @@
       <c r="K84">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L84" t="s">
+        <v>14</v>
+      </c>
+      <c r="M84" t="s">
+        <v>16</v>
+      </c>
+      <c r="N84">
+        <v>9.14177454565267E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>86</v>
       </c>
@@ -3364,8 +4158,17 @@
       <c r="K85">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L85" t="s">
+        <v>17</v>
+      </c>
+      <c r="M85" t="s">
+        <v>15</v>
+      </c>
+      <c r="N85">
+        <v>-0.26531298637648859</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>87</v>
       </c>
@@ -3399,8 +4202,17 @@
       <c r="K86">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L86" t="s">
+        <v>17</v>
+      </c>
+      <c r="M86" t="s">
+        <v>15</v>
+      </c>
+      <c r="N86">
+        <v>-0.36927684945685402</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>88</v>
       </c>
@@ -3434,8 +4246,17 @@
       <c r="K87">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L87" t="s">
+        <v>18</v>
+      </c>
+      <c r="M87" t="s">
+        <v>16</v>
+      </c>
+      <c r="N87">
+        <v>9.4189532068978954E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>89</v>
       </c>
@@ -3469,8 +4290,17 @@
       <c r="K88">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L88" t="s">
+        <v>17</v>
+      </c>
+      <c r="M88" t="s">
+        <v>15</v>
+      </c>
+      <c r="N88">
+        <v>-0.1059887191750324</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>90</v>
       </c>
@@ -3504,8 +4334,17 @@
       <c r="K89">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L89" t="s">
+        <v>17</v>
+      </c>
+      <c r="M89" t="s">
+        <v>16</v>
+      </c>
+      <c r="N89">
+        <v>-3.0211251354193221E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>91</v>
       </c>
@@ -3539,8 +4378,17 @@
       <c r="K90">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L90" t="s">
+        <v>14</v>
+      </c>
+      <c r="M90" t="s">
+        <v>15</v>
+      </c>
+      <c r="N90">
+        <v>4.0092569353150531E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>92</v>
       </c>
@@ -3574,8 +4422,17 @@
       <c r="K91">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L91" t="s">
+        <v>14</v>
+      </c>
+      <c r="M91" t="s">
+        <v>15</v>
+      </c>
+      <c r="N91">
+        <v>-0.13015862802296399</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>93</v>
       </c>
@@ -3609,8 +4466,17 @@
       <c r="K92">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L92" t="s">
+        <v>14</v>
+      </c>
+      <c r="M92" t="s">
+        <v>15</v>
+      </c>
+      <c r="N92">
+        <v>0.1122031738340636</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>94</v>
       </c>
@@ -3644,8 +4510,17 @@
       <c r="K93">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L93" t="s">
+        <v>14</v>
+      </c>
+      <c r="M93" t="s">
+        <v>16</v>
+      </c>
+      <c r="N93">
+        <v>0.18795780325797809</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>95</v>
       </c>
@@ -3679,8 +4554,17 @@
       <c r="K94">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L94" t="s">
+        <v>14</v>
+      </c>
+      <c r="M94" t="s">
+        <v>16</v>
+      </c>
+      <c r="N94">
+        <v>-0.1364913825938171</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>96</v>
       </c>
@@ -3714,8 +4598,17 @@
       <c r="K95">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L95" t="s">
+        <v>17</v>
+      </c>
+      <c r="M95" t="s">
+        <v>15</v>
+      </c>
+      <c r="N95">
+        <v>-0.3159119275867085</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>97</v>
       </c>
@@ -3749,8 +4642,17 @@
       <c r="K96">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L96" t="s">
+        <v>17</v>
+      </c>
+      <c r="M96" t="s">
+        <v>15</v>
+      </c>
+      <c r="N96">
+        <v>8.1510020915899428E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>98</v>
       </c>
@@ -3784,8 +4686,17 @@
       <c r="K97">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L97" t="s">
+        <v>18</v>
+      </c>
+      <c r="M97" t="s">
+        <v>15</v>
+      </c>
+      <c r="N97">
+        <v>-0.19164697379525389</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>99</v>
       </c>
@@ -3819,8 +4730,17 @@
       <c r="K98">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L98" t="s">
+        <v>18</v>
+      </c>
+      <c r="M98" t="s">
+        <v>16</v>
+      </c>
+      <c r="N98">
+        <v>0.1555420812230672</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>100</v>
       </c>
@@ -3854,8 +4774,17 @@
       <c r="K99">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L99" t="s">
+        <v>18</v>
+      </c>
+      <c r="M99" t="s">
+        <v>16</v>
+      </c>
+      <c r="N99">
+        <v>-0.2027014923145094</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>101</v>
       </c>
@@ -3889,8 +4818,17 @@
       <c r="K100">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L100" t="s">
+        <v>17</v>
+      </c>
+      <c r="M100" t="s">
+        <v>15</v>
+      </c>
+      <c r="N100">
+        <v>0.2322359535251215</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>102</v>
       </c>
@@ -3924,8 +4862,17 @@
       <c r="K101">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L101" t="s">
+        <v>17</v>
+      </c>
+      <c r="M101" t="s">
+        <v>15</v>
+      </c>
+      <c r="N101">
+        <v>1.9476440061626299E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>103</v>
       </c>
@@ -3959,8 +4906,17 @@
       <c r="K102">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L102" t="s">
+        <v>18</v>
+      </c>
+      <c r="M102" t="s">
+        <v>15</v>
+      </c>
+      <c r="N102">
+        <v>-0.20775640738152351</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>104</v>
       </c>
@@ -3994,8 +4950,17 @@
       <c r="K103">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L103" t="s">
+        <v>14</v>
+      </c>
+      <c r="M103" t="s">
+        <v>16</v>
+      </c>
+      <c r="N103">
+        <v>5.6177833806954069E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>105</v>
       </c>
@@ -4029,8 +4994,17 @@
       <c r="K104">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L104" t="s">
+        <v>14</v>
+      </c>
+      <c r="M104" t="s">
+        <v>16</v>
+      </c>
+      <c r="N104">
+        <v>2.8704792095781358E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>106</v>
       </c>
@@ -4064,8 +5038,17 @@
       <c r="K105">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L105" t="s">
+        <v>17</v>
+      </c>
+      <c r="M105" t="s">
+        <v>15</v>
+      </c>
+      <c r="N105">
+        <v>0.2000898865510351</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>107</v>
       </c>
@@ -4099,8 +5082,17 @@
       <c r="K106">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L106" t="s">
+        <v>17</v>
+      </c>
+      <c r="M106" t="s">
+        <v>15</v>
+      </c>
+      <c r="N106">
+        <v>-8.6504743438026277E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>108</v>
       </c>
@@ -4134,8 +5126,17 @@
       <c r="K107">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L107" t="s">
+        <v>18</v>
+      </c>
+      <c r="M107" t="s">
+        <v>16</v>
+      </c>
+      <c r="N107">
+        <v>0.1607044363959815</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>109</v>
       </c>
@@ -4169,8 +5170,17 @@
       <c r="K108">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L108" t="s">
+        <v>17</v>
+      </c>
+      <c r="M108" t="s">
+        <v>15</v>
+      </c>
+      <c r="N108">
+        <v>-0.13211908832966371</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>110</v>
       </c>
@@ -4204,8 +5214,17 @@
       <c r="K109">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L109" t="s">
+        <v>17</v>
+      </c>
+      <c r="M109" t="s">
+        <v>16</v>
+      </c>
+      <c r="N109">
+        <v>5.7861143409659421E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>111</v>
       </c>
@@ -4239,8 +5258,17 @@
       <c r="K110">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L110" t="s">
+        <v>14</v>
+      </c>
+      <c r="M110" t="s">
+        <v>15</v>
+      </c>
+      <c r="N110">
+        <v>6.3172561095536151E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>112</v>
       </c>
@@ -4274,8 +5302,17 @@
       <c r="K111">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L111" t="s">
+        <v>14</v>
+      </c>
+      <c r="M111" t="s">
+        <v>15</v>
+      </c>
+      <c r="N111">
+        <v>-0.17539701600948221</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>113</v>
       </c>
@@ -4309,8 +5346,17 @@
       <c r="K112">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L112" t="s">
+        <v>14</v>
+      </c>
+      <c r="M112" t="s">
+        <v>15</v>
+      </c>
+      <c r="N112">
+        <v>-5.9435050408550023E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>114</v>
       </c>
@@ -4344,8 +5390,17 @@
       <c r="K113">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L113" t="s">
+        <v>14</v>
+      </c>
+      <c r="M113" t="s">
+        <v>16</v>
+      </c>
+      <c r="N113">
+        <v>5.0147657198519317E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>115</v>
       </c>
@@ -4379,8 +5434,17 @@
       <c r="K114">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L114" t="s">
+        <v>14</v>
+      </c>
+      <c r="M114" t="s">
+        <v>16</v>
+      </c>
+      <c r="N114">
+        <v>-5.5492974886641948E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>116</v>
       </c>
@@ -4414,8 +5478,17 @@
       <c r="K115">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L115" t="s">
+        <v>17</v>
+      </c>
+      <c r="M115" t="s">
+        <v>15</v>
+      </c>
+      <c r="N115">
+        <v>-0.10778719401666539</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>117</v>
       </c>
@@ -4449,8 +5522,17 @@
       <c r="K116">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L116" t="s">
+        <v>17</v>
+      </c>
+      <c r="M116" t="s">
+        <v>15</v>
+      </c>
+      <c r="N116">
+        <v>-0.13296725447491139</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>118</v>
       </c>
@@ -4484,8 +5566,17 @@
       <c r="K117">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L117" t="s">
+        <v>18</v>
+      </c>
+      <c r="M117" t="s">
+        <v>15</v>
+      </c>
+      <c r="N117">
+        <v>-0.44658513843820358</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>119</v>
       </c>
@@ -4519,8 +5610,17 @@
       <c r="K118">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L118" t="s">
+        <v>18</v>
+      </c>
+      <c r="M118" t="s">
+        <v>16</v>
+      </c>
+      <c r="N118">
+        <v>-0.17777338486975461</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>120</v>
       </c>
@@ -4554,8 +5654,17 @@
       <c r="K119">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L119" t="s">
+        <v>18</v>
+      </c>
+      <c r="M119" t="s">
+        <v>16</v>
+      </c>
+      <c r="N119">
+        <v>0.1309479720529618</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>121</v>
       </c>
@@ -4589,8 +5698,17 @@
       <c r="K120">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L120" t="s">
+        <v>17</v>
+      </c>
+      <c r="M120" t="s">
+        <v>15</v>
+      </c>
+      <c r="N120">
+        <v>0.21213784588260881</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>122</v>
       </c>
@@ -4624,8 +5742,17 @@
       <c r="K121">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L121" t="s">
+        <v>17</v>
+      </c>
+      <c r="M121" t="s">
+        <v>15</v>
+      </c>
+      <c r="N121">
+        <v>-1.266554020636468E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>123</v>
       </c>
@@ -4659,8 +5786,17 @@
       <c r="K122">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L122" t="s">
+        <v>18</v>
+      </c>
+      <c r="M122" t="s">
+        <v>15</v>
+      </c>
+      <c r="N122">
+        <v>-3.265885952503933E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>124</v>
       </c>
@@ -4694,8 +5830,17 @@
       <c r="K123">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L123" t="s">
+        <v>14</v>
+      </c>
+      <c r="M123" t="s">
+        <v>16</v>
+      </c>
+      <c r="N123">
+        <v>-0.20110417130724581</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>125</v>
       </c>
@@ -4729,8 +5874,17 @@
       <c r="K124">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L124" t="s">
+        <v>14</v>
+      </c>
+      <c r="M124" t="s">
+        <v>16</v>
+      </c>
+      <c r="N124">
+        <v>6.7218002312282699E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>126</v>
       </c>
@@ -4764,8 +5918,17 @@
       <c r="K125">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L125" t="s">
+        <v>17</v>
+      </c>
+      <c r="M125" t="s">
+        <v>15</v>
+      </c>
+      <c r="N125">
+        <v>0.27952514626956632</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>127</v>
       </c>
@@ -4799,8 +5962,17 @@
       <c r="K126">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L126" t="s">
+        <v>17</v>
+      </c>
+      <c r="M126" t="s">
+        <v>15</v>
+      </c>
+      <c r="N126">
+        <v>0.18360175615001481</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>128</v>
       </c>
@@ -4834,8 +6006,17 @@
       <c r="K127">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L127" t="s">
+        <v>18</v>
+      </c>
+      <c r="M127" t="s">
+        <v>16</v>
+      </c>
+      <c r="N127">
+        <v>0.25494136221020858</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>129</v>
       </c>
@@ -4869,8 +6050,17 @@
       <c r="K128">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L128" t="s">
+        <v>17</v>
+      </c>
+      <c r="M128" t="s">
+        <v>15</v>
+      </c>
+      <c r="N128">
+        <v>0.1636180892152245</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>130</v>
       </c>
@@ -4904,8 +6094,17 @@
       <c r="K129">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L129" t="s">
+        <v>17</v>
+      </c>
+      <c r="M129" t="s">
+        <v>16</v>
+      </c>
+      <c r="N129">
+        <v>-3.2058250057393163E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>131</v>
       </c>
@@ -4939,8 +6138,17 @@
       <c r="K130">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L130" t="s">
+        <v>14</v>
+      </c>
+      <c r="M130" t="s">
+        <v>15</v>
+      </c>
+      <c r="N130">
+        <v>-0.24609044035798849</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>132</v>
       </c>
@@ -4974,8 +6182,17 @@
       <c r="K131">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L131" t="s">
+        <v>14</v>
+      </c>
+      <c r="M131" t="s">
+        <v>15</v>
+      </c>
+      <c r="N131">
+        <v>-0.46151018682575112</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>133</v>
       </c>
@@ -5009,8 +6226,17 @@
       <c r="K132">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L132" t="s">
+        <v>14</v>
+      </c>
+      <c r="M132" t="s">
+        <v>15</v>
+      </c>
+      <c r="N132">
+        <v>-0.21839970538246059</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>134</v>
       </c>
@@ -5044,8 +6270,17 @@
       <c r="K133">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L133" t="s">
+        <v>14</v>
+      </c>
+      <c r="M133" t="s">
+        <v>16</v>
+      </c>
+      <c r="N133">
+        <v>-0.2183034451701942</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>135</v>
       </c>
@@ -5079,8 +6314,17 @@
       <c r="K134">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L134" t="s">
+        <v>14</v>
+      </c>
+      <c r="M134" t="s">
+        <v>16</v>
+      </c>
+      <c r="N134">
+        <v>-3.3697290840886462E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>136</v>
       </c>
@@ -5114,8 +6358,17 @@
       <c r="K135">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L135" t="s">
+        <v>17</v>
+      </c>
+      <c r="M135" t="s">
+        <v>15</v>
+      </c>
+      <c r="N135">
+        <v>0.25036591519295209</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>137</v>
       </c>
@@ -5149,8 +6402,17 @@
       <c r="K136">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L136" t="s">
+        <v>17</v>
+      </c>
+      <c r="M136" t="s">
+        <v>15</v>
+      </c>
+      <c r="N136">
+        <v>0.22196007853246699</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>138</v>
       </c>
@@ -5184,8 +6446,17 @@
       <c r="K137">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L137" t="s">
+        <v>18</v>
+      </c>
+      <c r="M137" t="s">
+        <v>15</v>
+      </c>
+      <c r="N137">
+        <v>0.26327104900500581</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>139</v>
       </c>
@@ -5219,8 +6490,17 @@
       <c r="K138">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L138" t="s">
+        <v>18</v>
+      </c>
+      <c r="M138" t="s">
+        <v>16</v>
+      </c>
+      <c r="N138">
+        <v>-0.29551230040751708</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>140</v>
       </c>
@@ -5254,8 +6534,17 @@
       <c r="K139">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L139" t="s">
+        <v>18</v>
+      </c>
+      <c r="M139" t="s">
+        <v>16</v>
+      </c>
+      <c r="N139">
+        <v>0.2094109679516423</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>141</v>
       </c>
@@ -5289,8 +6578,17 @@
       <c r="K140">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L140" t="s">
+        <v>17</v>
+      </c>
+      <c r="M140" t="s">
+        <v>15</v>
+      </c>
+      <c r="N140">
+        <v>-5.8085416537931867E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>143</v>
       </c>
@@ -5324,8 +6622,17 @@
       <c r="K141">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L141" t="s">
+        <v>18</v>
+      </c>
+      <c r="M141" t="s">
+        <v>15</v>
+      </c>
+      <c r="N141">
+        <v>-0.16256121550053279</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>144</v>
       </c>
@@ -5359,8 +6666,17 @@
       <c r="K142">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L142" t="s">
+        <v>14</v>
+      </c>
+      <c r="M142" t="s">
+        <v>16</v>
+      </c>
+      <c r="N142">
+        <v>-0.19278192584830739</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>145</v>
       </c>
@@ -5394,8 +6710,17 @@
       <c r="K143">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L143" t="s">
+        <v>14</v>
+      </c>
+      <c r="M143" t="s">
+        <v>16</v>
+      </c>
+      <c r="N143">
+        <v>0.28399749913719807</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>146</v>
       </c>
@@ -5429,8 +6754,17 @@
       <c r="K144">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L144" t="s">
+        <v>17</v>
+      </c>
+      <c r="M144" t="s">
+        <v>15</v>
+      </c>
+      <c r="N144">
+        <v>0.51585833278113769</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>147</v>
       </c>
@@ -5464,8 +6798,17 @@
       <c r="K145">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L145" t="s">
+        <v>17</v>
+      </c>
+      <c r="M145" t="s">
+        <v>15</v>
+      </c>
+      <c r="N145">
+        <v>-0.46071568106766392</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>148</v>
       </c>
@@ -5499,8 +6842,17 @@
       <c r="K146">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L146" t="s">
+        <v>18</v>
+      </c>
+      <c r="M146" t="s">
+        <v>16</v>
+      </c>
+      <c r="N146">
+        <v>-0.33800886836435989</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>149</v>
       </c>
@@ -5534,8 +6886,17 @@
       <c r="K147">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L147" t="s">
+        <v>17</v>
+      </c>
+      <c r="M147" t="s">
+        <v>15</v>
+      </c>
+      <c r="N147">
+        <v>-0.47618570445435687</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>150</v>
       </c>
@@ -5569,8 +6930,17 @@
       <c r="K148">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L148" t="s">
+        <v>17</v>
+      </c>
+      <c r="M148" t="s">
+        <v>16</v>
+      </c>
+      <c r="N148">
+        <v>0.19040299613755921</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>151</v>
       </c>
@@ -5604,8 +6974,17 @@
       <c r="K149">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L149" t="s">
+        <v>14</v>
+      </c>
+      <c r="M149" t="s">
+        <v>15</v>
+      </c>
+      <c r="N149">
+        <v>0.43917087015794681</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>152</v>
       </c>
@@ -5639,8 +7018,17 @@
       <c r="K150">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L150" t="s">
+        <v>14</v>
+      </c>
+      <c r="M150" t="s">
+        <v>15</v>
+      </c>
+      <c r="N150">
+        <v>0.43431487567825439</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>153</v>
       </c>
@@ -5674,8 +7062,17 @@
       <c r="K151">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L151" t="s">
+        <v>14</v>
+      </c>
+      <c r="M151" t="s">
+        <v>15</v>
+      </c>
+      <c r="N151">
+        <v>5.8628193436597982E-2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>154</v>
       </c>
@@ -5709,8 +7106,17 @@
       <c r="K152">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L152" t="s">
+        <v>14</v>
+      </c>
+      <c r="M152" t="s">
+        <v>16</v>
+      </c>
+      <c r="N152">
+        <v>0.2033379529192573</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>155</v>
       </c>
@@ -5744,8 +7150,17 @@
       <c r="K153">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L153" t="s">
+        <v>14</v>
+      </c>
+      <c r="M153" t="s">
+        <v>16</v>
+      </c>
+      <c r="N153">
+        <v>2.8678468884401179E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>156</v>
       </c>
@@ -5779,8 +7194,17 @@
       <c r="K154">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L154" t="s">
+        <v>17</v>
+      </c>
+      <c r="M154" t="s">
+        <v>15</v>
+      </c>
+      <c r="N154">
+        <v>2.9172235064147681E-2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>157</v>
       </c>
@@ -5814,8 +7238,17 @@
       <c r="K155">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L155" t="s">
+        <v>17</v>
+      </c>
+      <c r="M155" t="s">
+        <v>15</v>
+      </c>
+      <c r="N155">
+        <v>-3.8323093777214427E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>158</v>
       </c>
@@ -5849,8 +7282,17 @@
       <c r="K156">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L156" t="s">
+        <v>18</v>
+      </c>
+      <c r="M156" t="s">
+        <v>15</v>
+      </c>
+      <c r="N156">
+        <v>0.1135383914939785</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>159</v>
       </c>
@@ -5884,8 +7326,17 @@
       <c r="K157">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L157" t="s">
+        <v>18</v>
+      </c>
+      <c r="M157" t="s">
+        <v>16</v>
+      </c>
+      <c r="N157">
+        <v>8.0896475398964496E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>160</v>
       </c>
@@ -5919,8 +7370,17 @@
       <c r="K158">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L158" t="s">
+        <v>18</v>
+      </c>
+      <c r="M158" t="s">
+        <v>16</v>
+      </c>
+      <c r="N158">
+        <v>2.834214527687073E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>161</v>
       </c>
@@ -5954,8 +7414,17 @@
       <c r="K159">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L159" t="s">
+        <v>17</v>
+      </c>
+      <c r="M159" t="s">
+        <v>15</v>
+      </c>
+      <c r="N159">
+        <v>-0.12049148187680631</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>162</v>
       </c>
@@ -5989,8 +7458,17 @@
       <c r="K160">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L160" t="s">
+        <v>17</v>
+      </c>
+      <c r="M160" t="s">
+        <v>15</v>
+      </c>
+      <c r="N160">
+        <v>-1.3741436578645461E-2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>163</v>
       </c>
@@ -6024,8 +7502,17 @@
       <c r="K161">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L161" t="s">
+        <v>18</v>
+      </c>
+      <c r="M161" t="s">
+        <v>15</v>
+      </c>
+      <c r="N161">
+        <v>0.1209324825606167</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>164</v>
       </c>
@@ -6059,8 +7546,17 @@
       <c r="K162">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L162" t="s">
+        <v>14</v>
+      </c>
+      <c r="M162" t="s">
+        <v>16</v>
+      </c>
+      <c r="N162">
+        <v>5.5975061913995261E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>165</v>
       </c>
@@ -6094,8 +7590,17 @@
       <c r="K163">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L163" t="s">
+        <v>14</v>
+      </c>
+      <c r="M163" t="s">
+        <v>16</v>
+      </c>
+      <c r="N163">
+        <v>1.6439727109711529E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>166</v>
       </c>
@@ -6129,8 +7634,17 @@
       <c r="K164">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L164" t="s">
+        <v>17</v>
+      </c>
+      <c r="M164" t="s">
+        <v>15</v>
+      </c>
+      <c r="N164">
+        <v>-0.2463449253732517</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>167</v>
       </c>
@@ -6164,8 +7678,17 @@
       <c r="K165">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L165" t="s">
+        <v>17</v>
+      </c>
+      <c r="M165" t="s">
+        <v>15</v>
+      </c>
+      <c r="N165">
+        <v>3.3466810670189862E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>168</v>
       </c>
@@ -6199,8 +7722,17 @@
       <c r="K166">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L166" t="s">
+        <v>18</v>
+      </c>
+      <c r="M166" t="s">
+        <v>16</v>
+      </c>
+      <c r="N166">
+        <v>-0.2482313564084874</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>169</v>
       </c>
@@ -6234,8 +7766,17 @@
       <c r="K167">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L167" t="s">
+        <v>17</v>
+      </c>
+      <c r="M167" t="s">
+        <v>15</v>
+      </c>
+      <c r="N167">
+        <v>-0.19361468215924951</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>170</v>
       </c>
@@ -6269,8 +7810,17 @@
       <c r="K168">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L168" t="s">
+        <v>17</v>
+      </c>
+      <c r="M168" t="s">
+        <v>16</v>
+      </c>
+      <c r="N168">
+        <v>-0.46404656622326818</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>171</v>
       </c>
@@ -6304,8 +7854,17 @@
       <c r="K169">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L169" t="s">
+        <v>14</v>
+      </c>
+      <c r="M169" t="s">
+        <v>15</v>
+      </c>
+      <c r="N169">
+        <v>0.2921892424300554</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>172</v>
       </c>
@@ -6339,8 +7898,17 @@
       <c r="K170">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L170" t="s">
+        <v>14</v>
+      </c>
+      <c r="M170" t="s">
+        <v>15</v>
+      </c>
+      <c r="N170">
+        <v>0.10220923093333301</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>173</v>
       </c>
@@ -6374,8 +7942,17 @@
       <c r="K171">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L171" t="s">
+        <v>14</v>
+      </c>
+      <c r="M171" t="s">
+        <v>15</v>
+      </c>
+      <c r="N171">
+        <v>5.9236040192385597E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>174</v>
       </c>
@@ -6409,8 +7986,17 @@
       <c r="K172">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L172" t="s">
+        <v>14</v>
+      </c>
+      <c r="M172" t="s">
+        <v>16</v>
+      </c>
+      <c r="N172">
+        <v>0.111813046222764</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>175</v>
       </c>
@@ -6444,8 +8030,17 @@
       <c r="K173">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L173" t="s">
+        <v>14</v>
+      </c>
+      <c r="M173" t="s">
+        <v>16</v>
+      </c>
+      <c r="N173">
+        <v>6.37350035343488E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>176</v>
       </c>
@@ -6479,8 +8074,17 @@
       <c r="K174">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L174" t="s">
+        <v>17</v>
+      </c>
+      <c r="M174" t="s">
+        <v>15</v>
+      </c>
+      <c r="N174">
+        <v>-0.21574682771882461</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>177</v>
       </c>
@@ -6514,8 +8118,17 @@
       <c r="K175">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L175" t="s">
+        <v>17</v>
+      </c>
+      <c r="M175" t="s">
+        <v>15</v>
+      </c>
+      <c r="N175">
+        <v>6.6763463221059305E-2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>178</v>
       </c>
@@ -6549,8 +8162,17 @@
       <c r="K176">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L176" t="s">
+        <v>18</v>
+      </c>
+      <c r="M176" t="s">
+        <v>15</v>
+      </c>
+      <c r="N176">
+        <v>-0.42946281340256898</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>179</v>
       </c>
@@ -6584,8 +8206,17 @@
       <c r="K177">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L177" t="s">
+        <v>18</v>
+      </c>
+      <c r="M177" t="s">
+        <v>16</v>
+      </c>
+      <c r="N177">
+        <v>5.2420938746558177E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>180</v>
       </c>
@@ -6619,8 +8250,17 @@
       <c r="K178">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L178" t="s">
+        <v>18</v>
+      </c>
+      <c r="M178" t="s">
+        <v>16</v>
+      </c>
+      <c r="N178">
+        <v>-3.3607366771435392E-3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>181</v>
       </c>
@@ -6654,8 +8294,17 @@
       <c r="K179">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L179" t="s">
+        <v>17</v>
+      </c>
+      <c r="M179" t="s">
+        <v>15</v>
+      </c>
+      <c r="N179">
+        <v>-0.48155255764729171</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>182</v>
       </c>
@@ -6689,8 +8338,17 @@
       <c r="K180">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L180" t="s">
+        <v>17</v>
+      </c>
+      <c r="M180" t="s">
+        <v>15</v>
+      </c>
+      <c r="N180">
+        <v>-7.0943278406164878E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>183</v>
       </c>
@@ -6724,8 +8382,17 @@
       <c r="K181">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L181" t="s">
+        <v>18</v>
+      </c>
+      <c r="M181" t="s">
+        <v>15</v>
+      </c>
+      <c r="N181">
+        <v>0.10472515376602939</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>184</v>
       </c>
@@ -6759,8 +8426,17 @@
       <c r="K182">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L182" t="s">
+        <v>14</v>
+      </c>
+      <c r="M182" t="s">
+        <v>16</v>
+      </c>
+      <c r="N182">
+        <v>0.22836015039595589</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>185</v>
       </c>
@@ -6794,8 +8470,17 @@
       <c r="K183">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L183" t="s">
+        <v>14</v>
+      </c>
+      <c r="M183" t="s">
+        <v>16</v>
+      </c>
+      <c r="N183">
+        <v>5.8389997172780261E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>186</v>
       </c>
@@ -6829,8 +8514,17 @@
       <c r="K184">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L184" t="s">
+        <v>17</v>
+      </c>
+      <c r="M184" t="s">
+        <v>15</v>
+      </c>
+      <c r="N184">
+        <v>3.6725614278483858E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>187</v>
       </c>
@@ -6864,8 +8558,17 @@
       <c r="K185">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L185" t="s">
+        <v>17</v>
+      </c>
+      <c r="M185" t="s">
+        <v>15</v>
+      </c>
+      <c r="N185">
+        <v>0.1212604766223776</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>188</v>
       </c>
@@ -6899,8 +8602,17 @@
       <c r="K186">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L186" t="s">
+        <v>18</v>
+      </c>
+      <c r="M186" t="s">
+        <v>16</v>
+      </c>
+      <c r="N186">
+        <v>1.1011239563905369E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>189</v>
       </c>
@@ -6934,8 +8646,17 @@
       <c r="K187">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L187" t="s">
+        <v>17</v>
+      </c>
+      <c r="M187" t="s">
+        <v>15</v>
+      </c>
+      <c r="N187">
+        <v>-1.09594690551118E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>190</v>
       </c>
@@ -6969,8 +8690,17 @@
       <c r="K188">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L188" t="s">
+        <v>17</v>
+      </c>
+      <c r="M188" t="s">
+        <v>16</v>
+      </c>
+      <c r="N188">
+        <v>0.17969624350400129</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>191</v>
       </c>
@@ -7004,8 +8734,17 @@
       <c r="K189">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L189" t="s">
+        <v>14</v>
+      </c>
+      <c r="M189" t="s">
+        <v>15</v>
+      </c>
+      <c r="N189">
+        <v>0.1213869981774881</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>192</v>
       </c>
@@ -7039,8 +8778,17 @@
       <c r="K190">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L190" t="s">
+        <v>14</v>
+      </c>
+      <c r="M190" t="s">
+        <v>15</v>
+      </c>
+      <c r="N190">
+        <v>-4.8302176798432288E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>193</v>
       </c>
@@ -7074,8 +8822,17 @@
       <c r="K191">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L191" t="s">
+        <v>14</v>
+      </c>
+      <c r="M191" t="s">
+        <v>15</v>
+      </c>
+      <c r="N191">
+        <v>-7.8887329891670133E-2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>194</v>
       </c>
@@ -7109,8 +8866,17 @@
       <c r="K192">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L192" t="s">
+        <v>14</v>
+      </c>
+      <c r="M192" t="s">
+        <v>16</v>
+      </c>
+      <c r="N192">
+        <v>2.858865358298723E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>195</v>
       </c>
@@ -7144,8 +8910,17 @@
       <c r="K193">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L193" t="s">
+        <v>14</v>
+      </c>
+      <c r="M193" t="s">
+        <v>16</v>
+      </c>
+      <c r="N193">
+        <v>0.13639546413590101</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>196</v>
       </c>
@@ -7179,8 +8954,17 @@
       <c r="K194">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L194" t="s">
+        <v>17</v>
+      </c>
+      <c r="M194" t="s">
+        <v>15</v>
+      </c>
+      <c r="N194">
+        <v>0.13385353745010059</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>197</v>
       </c>
@@ -7214,8 +8998,17 @@
       <c r="K195">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L195" t="s">
+        <v>17</v>
+      </c>
+      <c r="M195" t="s">
+        <v>15</v>
+      </c>
+      <c r="N195">
+        <v>-3.8079520935042521E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>198</v>
       </c>
@@ -7249,8 +9042,17 @@
       <c r="K196">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L196" t="s">
+        <v>18</v>
+      </c>
+      <c r="M196" t="s">
+        <v>15</v>
+      </c>
+      <c r="N196">
+        <v>-5.1708692978686743E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>199</v>
       </c>
@@ -7284,8 +9086,17 @@
       <c r="K197">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L197" t="s">
+        <v>18</v>
+      </c>
+      <c r="M197" t="s">
+        <v>16</v>
+      </c>
+      <c r="N197">
+        <v>-0.24110521437561469</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>200</v>
       </c>
@@ -7319,8 +9130,17 @@
       <c r="K198">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L198" t="s">
+        <v>18</v>
+      </c>
+      <c r="M198" t="s">
+        <v>16</v>
+      </c>
+      <c r="N198">
+        <v>0.13193887976159371</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>201</v>
       </c>
@@ -7354,8 +9174,17 @@
       <c r="K199">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L199" t="s">
+        <v>17</v>
+      </c>
+      <c r="M199" t="s">
+        <v>15</v>
+      </c>
+      <c r="N199">
+        <v>0.17330786039572749</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>202</v>
       </c>
@@ -7389,8 +9218,17 @@
       <c r="K200">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L200" t="s">
+        <v>17</v>
+      </c>
+      <c r="M200" t="s">
+        <v>15</v>
+      </c>
+      <c r="N200">
+        <v>-0.25773416145510658</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>203</v>
       </c>
@@ -7424,8 +9262,17 @@
       <c r="K201">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L201" t="s">
+        <v>18</v>
+      </c>
+      <c r="M201" t="s">
+        <v>15</v>
+      </c>
+      <c r="N201">
+        <v>-8.2916303525496393E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>204</v>
       </c>
@@ -7459,8 +9306,17 @@
       <c r="K202">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L202" t="s">
+        <v>14</v>
+      </c>
+      <c r="M202" t="s">
+        <v>16</v>
+      </c>
+      <c r="N202">
+        <v>0.100022528893925</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>205</v>
       </c>
@@ -7494,8 +9350,17 @@
       <c r="K203">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L203" t="s">
+        <v>14</v>
+      </c>
+      <c r="M203" t="s">
+        <v>16</v>
+      </c>
+      <c r="N203">
+        <v>-0.1229154225146626</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>206</v>
       </c>
@@ -7529,8 +9394,17 @@
       <c r="K204">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L204" t="s">
+        <v>17</v>
+      </c>
+      <c r="M204" t="s">
+        <v>15</v>
+      </c>
+      <c r="N204">
+        <v>0.22115628354510919</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>207</v>
       </c>
@@ -7564,8 +9438,17 @@
       <c r="K205">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L205" t="s">
+        <v>17</v>
+      </c>
+      <c r="M205" t="s">
+        <v>15</v>
+      </c>
+      <c r="N205">
+        <v>0.14607328443163581</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>208</v>
       </c>
@@ -7599,8 +9482,17 @@
       <c r="K206">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L206" t="s">
+        <v>18</v>
+      </c>
+      <c r="M206" t="s">
+        <v>16</v>
+      </c>
+      <c r="N206">
+        <v>0.13395429751026061</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>209</v>
       </c>
@@ -7634,8 +9526,17 @@
       <c r="K207">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L207" t="s">
+        <v>17</v>
+      </c>
+      <c r="M207" t="s">
+        <v>15</v>
+      </c>
+      <c r="N207">
+        <v>7.1841728220336409E-2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>210</v>
       </c>
@@ -7669,8 +9570,17 @@
       <c r="K208">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L208" t="s">
+        <v>17</v>
+      </c>
+      <c r="M208" t="s">
+        <v>16</v>
+      </c>
+      <c r="N208">
+        <v>-0.25637946693456931</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>211</v>
       </c>
@@ -7704,8 +9614,17 @@
       <c r="K209">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L209" t="s">
+        <v>14</v>
+      </c>
+      <c r="M209" t="s">
+        <v>15</v>
+      </c>
+      <c r="N209">
+        <v>-5.1678065553597663E-2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>212</v>
       </c>
@@ -7739,8 +9658,17 @@
       <c r="K210">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L210" t="s">
+        <v>14</v>
+      </c>
+      <c r="M210" t="s">
+        <v>15</v>
+      </c>
+      <c r="N210">
+        <v>8.5125136576630789E-2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>213</v>
       </c>
@@ -7774,8 +9702,17 @@
       <c r="K211">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L211" t="s">
+        <v>14</v>
+      </c>
+      <c r="M211" t="s">
+        <v>15</v>
+      </c>
+      <c r="N211">
+        <v>-7.980596249579075E-2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>214</v>
       </c>
@@ -7809,8 +9746,17 @@
       <c r="K212">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L212" t="s">
+        <v>14</v>
+      </c>
+      <c r="M212" t="s">
+        <v>16</v>
+      </c>
+      <c r="N212">
+        <v>-0.1934852979479133</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>215</v>
       </c>
@@ -7844,8 +9790,17 @@
       <c r="K213">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L213" t="s">
+        <v>14</v>
+      </c>
+      <c r="M213" t="s">
+        <v>16</v>
+      </c>
+      <c r="N213">
+        <v>-0.1431789268496135</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>216</v>
       </c>
@@ -7879,8 +9834,17 @@
       <c r="K214">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L214" t="s">
+        <v>17</v>
+      </c>
+      <c r="M214" t="s">
+        <v>15</v>
+      </c>
+      <c r="N214">
+        <v>0.2463412207302379</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>217</v>
       </c>
@@ -7914,8 +9878,17 @@
       <c r="K215">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L215" t="s">
+        <v>17</v>
+      </c>
+      <c r="M215" t="s">
+        <v>15</v>
+      </c>
+      <c r="N215">
+        <v>4.1691651228063953E-2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>218</v>
       </c>
@@ -7949,8 +9922,17 @@
       <c r="K216">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L216" t="s">
+        <v>18</v>
+      </c>
+      <c r="M216" t="s">
+        <v>15</v>
+      </c>
+      <c r="N216">
+        <v>0.1771743127715186</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>219</v>
       </c>
@@ -7984,8 +9966,17 @@
       <c r="K217">
         <v>-4.9962841659560802</v>
       </c>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L217" t="s">
+        <v>18</v>
+      </c>
+      <c r="M217" t="s">
+        <v>16</v>
+      </c>
+      <c r="N217">
+        <v>-0.45691357706182423</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>220</v>
       </c>
@@ -8019,8 +10010,17 @@
       <c r="K218">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L218" t="s">
+        <v>18</v>
+      </c>
+      <c r="M218" t="s">
+        <v>16</v>
+      </c>
+      <c r="N218">
+        <v>0.23935105342358109</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>221</v>
       </c>
@@ -8054,8 +10054,17 @@
       <c r="K219">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L219" t="s">
+        <v>17</v>
+      </c>
+      <c r="M219" t="s">
+        <v>15</v>
+      </c>
+      <c r="N219">
+        <v>-0.245048346328016</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>222</v>
       </c>
@@ -8089,8 +10098,17 @@
       <c r="K220">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L220" t="s">
+        <v>17</v>
+      </c>
+      <c r="M220" t="s">
+        <v>15</v>
+      </c>
+      <c r="N220">
+        <v>0.35469215070616977</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>223</v>
       </c>
@@ -8124,8 +10142,17 @@
       <c r="K221">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L221" t="s">
+        <v>18</v>
+      </c>
+      <c r="M221" t="s">
+        <v>15</v>
+      </c>
+      <c r="N221">
+        <v>-8.2386792107378981E-2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>224</v>
       </c>
@@ -8159,8 +10186,17 @@
       <c r="K222">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L222" t="s">
+        <v>14</v>
+      </c>
+      <c r="M222" t="s">
+        <v>16</v>
+      </c>
+      <c r="N222">
+        <v>-0.27500288492866448</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>225</v>
       </c>
@@ -8194,8 +10230,17 @@
       <c r="K223">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L223" t="s">
+        <v>14</v>
+      </c>
+      <c r="M223" t="s">
+        <v>16</v>
+      </c>
+      <c r="N223">
+        <v>-2.558495294491514E-2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>227</v>
       </c>
@@ -8229,8 +10274,17 @@
       <c r="K224">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L224" t="s">
+        <v>17</v>
+      </c>
+      <c r="M224" t="s">
+        <v>15</v>
+      </c>
+      <c r="N224">
+        <v>-0.25192236825827879</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>228</v>
       </c>
@@ -8264,8 +10318,17 @@
       <c r="K225">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L225" t="s">
+        <v>18</v>
+      </c>
+      <c r="M225" t="s">
+        <v>16</v>
+      </c>
+      <c r="N225">
+        <v>-0.14392083653471199</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>229</v>
       </c>
@@ -8299,8 +10362,17 @@
       <c r="K226">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L226" t="s">
+        <v>17</v>
+      </c>
+      <c r="M226" t="s">
+        <v>15</v>
+      </c>
+      <c r="N226">
+        <v>0.31924232066778391</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>230</v>
       </c>
@@ -8334,8 +10406,17 @@
       <c r="K227">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L227" t="s">
+        <v>17</v>
+      </c>
+      <c r="M227" t="s">
+        <v>16</v>
+      </c>
+      <c r="N227">
+        <v>0.35642881435221219</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>231</v>
       </c>
@@ -8369,8 +10450,17 @@
       <c r="K228">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L228" t="s">
+        <v>14</v>
+      </c>
+      <c r="M228" t="s">
+        <v>15</v>
+      </c>
+      <c r="N228">
+        <v>-9.0692282886359332E-2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>232</v>
       </c>
@@ -8404,8 +10494,17 @@
       <c r="K229">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L229" t="s">
+        <v>14</v>
+      </c>
+      <c r="M229" t="s">
+        <v>15</v>
+      </c>
+      <c r="N229">
+        <v>0.30446993387485127</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>233</v>
       </c>
@@ -8439,8 +10538,17 @@
       <c r="K230">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L230" t="s">
+        <v>14</v>
+      </c>
+      <c r="M230" t="s">
+        <v>15</v>
+      </c>
+      <c r="N230">
+        <v>0.16261774661912839</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>234</v>
       </c>
@@ -8474,8 +10582,17 @@
       <c r="K231">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L231" t="s">
+        <v>14</v>
+      </c>
+      <c r="M231" t="s">
+        <v>16</v>
+      </c>
+      <c r="N231">
+        <v>0.2991148342861818</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>235</v>
       </c>
@@ -8509,8 +10626,17 @@
       <c r="K232">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L232" t="s">
+        <v>14</v>
+      </c>
+      <c r="M232" t="s">
+        <v>16</v>
+      </c>
+      <c r="N232">
+        <v>0.32973374356728657</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>236</v>
       </c>
@@ -8544,8 +10670,17 @@
       <c r="K233">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L233" t="s">
+        <v>17</v>
+      </c>
+      <c r="M233" t="s">
+        <v>15</v>
+      </c>
+      <c r="N233">
+        <v>6.6147925208499214E-2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>237</v>
       </c>
@@ -8579,8 +10714,17 @@
       <c r="K234">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L234" t="s">
+        <v>17</v>
+      </c>
+      <c r="M234" t="s">
+        <v>15</v>
+      </c>
+      <c r="N234">
+        <v>-0.3022925792723169</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>238</v>
       </c>
@@ -8614,8 +10758,17 @@
       <c r="K235">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L235" t="s">
+        <v>18</v>
+      </c>
+      <c r="M235" t="s">
+        <v>15</v>
+      </c>
+      <c r="N235">
+        <v>0.315957811240413</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>240</v>
       </c>
@@ -8649,8 +10802,17 @@
       <c r="K236">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L236" t="s">
+        <v>18</v>
+      </c>
+      <c r="M236" t="s">
+        <v>16</v>
+      </c>
+      <c r="N236">
+        <v>0.2437214313755883</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>241</v>
       </c>
@@ -8684,8 +10846,17 @@
       <c r="K237">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L237" t="s">
+        <v>17</v>
+      </c>
+      <c r="M237" t="s">
+        <v>15</v>
+      </c>
+      <c r="N237">
+        <v>-0.28717805828007181</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>242</v>
       </c>
@@ -8719,8 +10890,17 @@
       <c r="K238">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L238" t="s">
+        <v>17</v>
+      </c>
+      <c r="M238" t="s">
+        <v>15</v>
+      </c>
+      <c r="N238">
+        <v>0.100751689651551</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>243</v>
       </c>
@@ -8754,8 +10934,17 @@
       <c r="K239">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L239" t="s">
+        <v>18</v>
+      </c>
+      <c r="M239" t="s">
+        <v>15</v>
+      </c>
+      <c r="N239">
+        <v>-0.17619951903647879</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>244</v>
       </c>
@@ -8789,8 +10978,17 @@
       <c r="K240">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L240" t="s">
+        <v>14</v>
+      </c>
+      <c r="M240" t="s">
+        <v>16</v>
+      </c>
+      <c r="N240">
+        <v>0.14072188513931269</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>245</v>
       </c>
@@ -8824,8 +11022,17 @@
       <c r="K241">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L241" t="s">
+        <v>14</v>
+      </c>
+      <c r="M241" t="s">
+        <v>16</v>
+      </c>
+      <c r="N241">
+        <v>-0.1828933689967519</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>246</v>
       </c>
@@ -8859,8 +11066,17 @@
       <c r="K242">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L242" t="s">
+        <v>17</v>
+      </c>
+      <c r="M242" t="s">
+        <v>15</v>
+      </c>
+      <c r="N242">
+        <v>-9.3662595984055186E-2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>247</v>
       </c>
@@ -8894,8 +11110,17 @@
       <c r="K243">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L243" t="s">
+        <v>17</v>
+      </c>
+      <c r="M243" t="s">
+        <v>15</v>
+      </c>
+      <c r="N243">
+        <v>0.1804260912165544</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>248</v>
       </c>
@@ -8929,8 +11154,17 @@
       <c r="K244">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L244" t="s">
+        <v>18</v>
+      </c>
+      <c r="M244" t="s">
+        <v>16</v>
+      </c>
+      <c r="N244">
+        <v>-0.5960454643312989</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>249</v>
       </c>
@@ -8964,8 +11198,17 @@
       <c r="K245">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L245" t="s">
+        <v>17</v>
+      </c>
+      <c r="M245" t="s">
+        <v>15</v>
+      </c>
+      <c r="N245">
+        <v>-0.33423474573081402</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>250</v>
       </c>
@@ -8999,8 +11242,17 @@
       <c r="K246">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L246" t="s">
+        <v>14</v>
+      </c>
+      <c r="M246" t="s">
+        <v>15</v>
+      </c>
+      <c r="N246">
+        <v>0.27224460121792993</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>251</v>
       </c>
@@ -9034,8 +11286,17 @@
       <c r="K247">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L247" t="s">
+        <v>14</v>
+      </c>
+      <c r="M247" t="s">
+        <v>15</v>
+      </c>
+      <c r="N247">
+        <v>-0.1187104269589265</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>252</v>
       </c>
@@ -9069,8 +11330,17 @@
       <c r="K248">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L248" t="s">
+        <v>14</v>
+      </c>
+      <c r="M248" t="s">
+        <v>15</v>
+      </c>
+      <c r="N248">
+        <v>0.1610624188683141</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>253</v>
       </c>
@@ -9104,8 +11374,17 @@
       <c r="K249">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L249" t="s">
+        <v>14</v>
+      </c>
+      <c r="M249" t="s">
+        <v>16</v>
+      </c>
+      <c r="N249">
+        <v>-3.9481228657798573E-2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>254</v>
       </c>
@@ -9139,8 +11418,17 @@
       <c r="K250">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L250" t="s">
+        <v>14</v>
+      </c>
+      <c r="M250" t="s">
+        <v>16</v>
+      </c>
+      <c r="N250">
+        <v>-0.17109330418466559</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>255</v>
       </c>
@@ -9174,8 +11462,17 @@
       <c r="K251">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L251" t="s">
+        <v>17</v>
+      </c>
+      <c r="M251" t="s">
+        <v>15</v>
+      </c>
+      <c r="N251">
+        <v>0.12642200724534791</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>256</v>
       </c>
@@ -9209,8 +11506,17 @@
       <c r="K252">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L252" t="s">
+        <v>17</v>
+      </c>
+      <c r="M252" t="s">
+        <v>15</v>
+      </c>
+      <c r="N252">
+        <v>0.19581163164087789</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>257</v>
       </c>
@@ -9244,8 +11550,17 @@
       <c r="K253">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L253" t="s">
+        <v>18</v>
+      </c>
+      <c r="M253" t="s">
+        <v>15</v>
+      </c>
+      <c r="N253">
+        <v>-0.18722206821905649</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>258</v>
       </c>
@@ -9279,8 +11594,17 @@
       <c r="K254">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L254" t="s">
+        <v>18</v>
+      </c>
+      <c r="M254" t="s">
+        <v>16</v>
+      </c>
+      <c r="N254">
+        <v>-3.015209707329802E-2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>259</v>
       </c>
@@ -9314,8 +11638,17 @@
       <c r="K255">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L255" t="s">
+        <v>17</v>
+      </c>
+      <c r="M255" t="s">
+        <v>15</v>
+      </c>
+      <c r="N255">
+        <v>-0.18933958934947809</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>260</v>
       </c>
@@ -9349,8 +11682,17 @@
       <c r="K256">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L256" t="s">
+        <v>17</v>
+      </c>
+      <c r="M256" t="s">
+        <v>15</v>
+      </c>
+      <c r="N256">
+        <v>-1.334661836414841E-2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>261</v>
       </c>
@@ -9384,8 +11726,17 @@
       <c r="K257">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L257" t="s">
+        <v>18</v>
+      </c>
+      <c r="M257" t="s">
+        <v>15</v>
+      </c>
+      <c r="N257">
+        <v>0.1099382217095809</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>262</v>
       </c>
@@ -9419,8 +11770,17 @@
       <c r="K258">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L258" t="s">
+        <v>14</v>
+      </c>
+      <c r="M258" t="s">
+        <v>16</v>
+      </c>
+      <c r="N258">
+        <v>0.22906851667277531</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>263</v>
       </c>
@@ -9454,8 +11814,17 @@
       <c r="K259">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L259" t="s">
+        <v>14</v>
+      </c>
+      <c r="M259" t="s">
+        <v>16</v>
+      </c>
+      <c r="N259">
+        <v>0.14215343263658589</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>264</v>
       </c>
@@ -9489,8 +11858,17 @@
       <c r="K260">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L260" t="s">
+        <v>17</v>
+      </c>
+      <c r="M260" t="s">
+        <v>15</v>
+      </c>
+      <c r="N260">
+        <v>-0.1344990176119196</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>265</v>
       </c>
@@ -9524,8 +11902,17 @@
       <c r="K261">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L261" t="s">
+        <v>17</v>
+      </c>
+      <c r="M261" t="s">
+        <v>15</v>
+      </c>
+      <c r="N261">
+        <v>7.8467180965924976E-2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>266</v>
       </c>
@@ -9559,8 +11946,17 @@
       <c r="K262">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L262" t="s">
+        <v>18</v>
+      </c>
+      <c r="M262" t="s">
+        <v>16</v>
+      </c>
+      <c r="N262">
+        <v>0.14501296095123789</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>267</v>
       </c>
@@ -9594,8 +11990,17 @@
       <c r="K263">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L263" t="s">
+        <v>17</v>
+      </c>
+      <c r="M263" t="s">
+        <v>15</v>
+      </c>
+      <c r="N263">
+        <v>7.6805227491056893E-3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>268</v>
       </c>
@@ -9629,8 +12034,17 @@
       <c r="K264">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L264" t="s">
+        <v>17</v>
+      </c>
+      <c r="M264" t="s">
+        <v>16</v>
+      </c>
+      <c r="N264">
+        <v>0.107004988186296</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>269</v>
       </c>
@@ -9664,8 +12078,17 @@
       <c r="K265">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L265" t="s">
+        <v>14</v>
+      </c>
+      <c r="M265" t="s">
+        <v>15</v>
+      </c>
+      <c r="N265">
+        <v>-8.448393834511847E-2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>270</v>
       </c>
@@ -9699,8 +12122,17 @@
       <c r="K266">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L266" t="s">
+        <v>14</v>
+      </c>
+      <c r="M266" t="s">
+        <v>15</v>
+      </c>
+      <c r="N266">
+        <v>0.115990006464017</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>271</v>
       </c>
@@ -9734,8 +12166,17 @@
       <c r="K267">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L267" t="s">
+        <v>14</v>
+      </c>
+      <c r="M267" t="s">
+        <v>15</v>
+      </c>
+      <c r="N267">
+        <v>-0.19720831605281169</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>272</v>
       </c>
@@ -9769,8 +12210,17 @@
       <c r="K268">
         <v>-10.48912528345827</v>
       </c>
-    </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L268" t="s">
+        <v>14</v>
+      </c>
+      <c r="M268" t="s">
+        <v>16</v>
+      </c>
+      <c r="N268">
+        <v>-0.36308064538075829</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>273</v>
       </c>
@@ -9804,8 +12254,17 @@
       <c r="K269">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L269" t="s">
+        <v>14</v>
+      </c>
+      <c r="M269" t="s">
+        <v>16</v>
+      </c>
+      <c r="N269">
+        <v>1.925953922169743E-2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>274</v>
       </c>
@@ -9839,8 +12298,17 @@
       <c r="K270">
         <v>-8.6880952261108906</v>
       </c>
-    </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L270" t="s">
+        <v>17</v>
+      </c>
+      <c r="M270" t="s">
+        <v>15</v>
+      </c>
+      <c r="N270">
+        <v>-8.3798927423267E-2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>275</v>
       </c>
@@ -9874,8 +12342,17 @@
       <c r="K271">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L271" t="s">
+        <v>17</v>
+      </c>
+      <c r="M271" t="s">
+        <v>15</v>
+      </c>
+      <c r="N271">
+        <v>4.4028220865912959E-2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>276</v>
       </c>
@@ -9909,8 +12386,17 @@
       <c r="K272">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L272" t="s">
+        <v>18</v>
+      </c>
+      <c r="M272" t="s">
+        <v>16</v>
+      </c>
+      <c r="N272">
+        <v>0.15099230815238809</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>277</v>
       </c>
@@ -9944,8 +12430,17 @@
       <c r="K273">
         <v>-1.885097133172676</v>
       </c>
-    </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L273" t="s">
+        <v>17</v>
+      </c>
+      <c r="M273" t="s">
+        <v>15</v>
+      </c>
+      <c r="N273">
+        <v>0.16782841026829301</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>278</v>
       </c>
@@ -9979,8 +12474,17 @@
       <c r="K274">
         <v>-1.6813816206799821</v>
       </c>
-    </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L274" t="s">
+        <v>17</v>
+      </c>
+      <c r="M274" t="s">
+        <v>15</v>
+      </c>
+      <c r="N274">
+        <v>-3.6533545137224073E-2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>279</v>
       </c>
@@ -10014,8 +12518,17 @@
       <c r="K275">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L275" t="s">
+        <v>18</v>
+      </c>
+      <c r="M275" t="s">
+        <v>15</v>
+      </c>
+      <c r="N275">
+        <v>7.1356070994934018E-2</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>280</v>
       </c>
@@ -10049,8 +12562,17 @@
       <c r="K276">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L276" t="s">
+        <v>14</v>
+      </c>
+      <c r="M276" t="s">
+        <v>16</v>
+      </c>
+      <c r="N276">
+        <v>-0.30273211105483039</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>281</v>
       </c>
@@ -10084,8 +12606,17 @@
       <c r="K277">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L277" t="s">
+        <v>14</v>
+      </c>
+      <c r="M277" t="s">
+        <v>16</v>
+      </c>
+      <c r="N277">
+        <v>-0.100462538254079</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>282</v>
       </c>
@@ -10119,8 +12650,17 @@
       <c r="K278">
         <v>3.0883660479607058</v>
       </c>
-    </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L278" t="s">
+        <v>17</v>
+      </c>
+      <c r="M278" t="s">
+        <v>15</v>
+      </c>
+      <c r="N278">
+        <v>-0.43044485948957051</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>283</v>
       </c>
@@ -10154,8 +12694,17 @@
       <c r="K279">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L279" t="s">
+        <v>17</v>
+      </c>
+      <c r="M279" t="s">
+        <v>15</v>
+      </c>
+      <c r="N279">
+        <v>0.29484717620656631</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>284</v>
       </c>
@@ -10189,8 +12738,17 @@
       <c r="K280">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L280" t="s">
+        <v>18</v>
+      </c>
+      <c r="M280" t="s">
+        <v>16</v>
+      </c>
+      <c r="N280">
+        <v>0.29263150018537509</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>285</v>
       </c>
@@ -10224,8 +12782,17 @@
       <c r="K281">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L281" t="s">
+        <v>17</v>
+      </c>
+      <c r="M281" t="s">
+        <v>15</v>
+      </c>
+      <c r="N281">
+        <v>0.23063029976579391</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>286</v>
       </c>
@@ -10259,8 +12826,17 @@
       <c r="K282">
         <v>9.271108922582119</v>
       </c>
-    </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L282" t="s">
+        <v>17</v>
+      </c>
+      <c r="M282" t="s">
+        <v>16</v>
+      </c>
+      <c r="N282">
+        <v>-4.9361153265659929E-2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>287</v>
       </c>
@@ -10294,8 +12870,17 @@
       <c r="K283">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L283" t="s">
+        <v>14</v>
+      </c>
+      <c r="M283" t="s">
+        <v>15</v>
+      </c>
+      <c r="N283">
+        <v>-0.26745193106266929</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>288</v>
       </c>
@@ -10329,8 +12914,17 @@
       <c r="K284">
         <v>17.999121975770219</v>
       </c>
-    </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L284" t="s">
+        <v>14</v>
+      </c>
+      <c r="M284" t="s">
+        <v>15</v>
+      </c>
+      <c r="N284">
+        <v>9.7317112498215286E-2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>289</v>
       </c>
@@ -10364,8 +12958,17 @@
       <c r="K285">
         <v>-7.1995630420446393</v>
       </c>
-    </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L285" t="s">
+        <v>14</v>
+      </c>
+      <c r="M285" t="s">
+        <v>15</v>
+      </c>
+      <c r="N285">
+        <v>0.1370723954086778</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>290</v>
       </c>
@@ -10399,8 +13002,17 @@
       <c r="K286">
         <v>-11.085206529097629</v>
       </c>
-    </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L286" t="s">
+        <v>14</v>
+      </c>
+      <c r="M286" t="s">
+        <v>16</v>
+      </c>
+      <c r="N286">
+        <v>-0.30365670200051098</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>292</v>
       </c>
@@ -10434,8 +13046,17 @@
       <c r="K287">
         <v>-8.5861877896217624</v>
       </c>
-    </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L287" t="s">
+        <v>17</v>
+      </c>
+      <c r="M287" t="s">
+        <v>15</v>
+      </c>
+      <c r="N287">
+        <v>1.1065432391768271E-2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>293</v>
       </c>
@@ -10469,8 +13090,17 @@
       <c r="K288">
         <v>-6.5018680891506371</v>
       </c>
-    </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L288" t="s">
+        <v>18</v>
+      </c>
+      <c r="M288" t="s">
+        <v>15</v>
+      </c>
+      <c r="N288">
+        <v>0.1530844284872841</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>294</v>
       </c>
@@ -10504,8 +13134,17 @@
       <c r="K289">
         <v>-3.6318170755179602</v>
       </c>
-    </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L289" t="s">
+        <v>18</v>
+      </c>
+      <c r="M289" t="s">
+        <v>16</v>
+      </c>
+      <c r="N289">
+        <v>-0.56370773146238939</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>296</v>
       </c>
@@ -10539,8 +13178,17 @@
       <c r="K290">
         <v>-0.70775605392083529</v>
       </c>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L290" t="s">
+        <v>18</v>
+      </c>
+      <c r="M290" t="s">
+        <v>15</v>
+      </c>
+      <c r="N290">
+        <v>4.7379332040030531E-2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>297</v>
       </c>
@@ -10574,8 +13222,17 @@
       <c r="K291">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L291" t="s">
+        <v>14</v>
+      </c>
+      <c r="M291" t="s">
+        <v>16</v>
+      </c>
+      <c r="N291">
+        <v>-0.41311620024831902</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>298</v>
       </c>
@@ -10609,8 +13266,17 @@
       <c r="K292">
         <v>2.0750570177482439</v>
       </c>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L292" t="s">
+        <v>14</v>
+      </c>
+      <c r="M292" t="s">
+        <v>16</v>
+      </c>
+      <c r="N292">
+        <v>-0.41708109260008569</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>299</v>
       </c>
@@ -10644,8 +13310,17 @@
       <c r="K293">
         <v>2.843881538175046</v>
       </c>
-    </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L293" t="s">
+        <v>14</v>
+      </c>
+      <c r="M293" t="s">
+        <v>16</v>
+      </c>
+      <c r="N293">
+        <v>-0.30388836031195859</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>301</v>
       </c>
@@ -10679,8 +13354,17 @@
       <c r="K294">
         <v>2.9346639027167112</v>
       </c>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L294" t="s">
+        <v>17</v>
+      </c>
+      <c r="M294" t="s">
+        <v>15</v>
+      </c>
+      <c r="N294">
+        <v>0.18723151099117269</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>302</v>
       </c>
@@ -10714,8 +13398,17 @@
       <c r="K295">
         <v>7.3722976610735058</v>
       </c>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L295" t="s">
+        <v>18</v>
+      </c>
+      <c r="M295" t="s">
+        <v>16</v>
+      </c>
+      <c r="N295">
+        <v>5.44464077612965E-2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>303</v>
       </c>
@@ -10749,8 +13442,17 @@
       <c r="K296">
         <v>9.5877356681982047</v>
       </c>
-    </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L296" t="s">
+        <v>17</v>
+      </c>
+      <c r="M296" t="s">
+        <v>15</v>
+      </c>
+      <c r="N296">
+        <v>0.36889913655700629</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>304</v>
       </c>
@@ -10784,8 +13486,17 @@
       <c r="K297">
         <v>18.256757843242958</v>
       </c>
-    </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L297" t="s">
+        <v>14</v>
+      </c>
+      <c r="M297" t="s">
+        <v>15</v>
+      </c>
+      <c r="N297">
+        <v>-0.27899523946504379</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>305</v>
       </c>
@@ -10818,6 +13529,15 @@
       </c>
       <c r="K298">
         <v>17.999121975770219</v>
+      </c>
+      <c r="L298" t="s">
+        <v>14</v>
+      </c>
+      <c r="M298" t="s">
+        <v>15</v>
+      </c>
+      <c r="N298">
+        <v>-1.311656762962332E-2</v>
       </c>
     </row>
   </sheetData>
